--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/36.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/36.xlsx
@@ -426,13 +426,13 @@
         <v>-15.46697942409542</v>
       </c>
       <c r="E2">
-        <v>-4.77473792791803</v>
+        <v>-6.866494505245275</v>
       </c>
       <c r="F2">
-        <v>2.314744162928277</v>
+        <v>2.943398811852044</v>
       </c>
       <c r="G2">
-        <v>-16.04139194748032</v>
+        <v>-19.0144282601301</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-14.6074538210739</v>
       </c>
       <c r="E3">
-        <v>-5.614459112839813</v>
+        <v>-6.552956122699994</v>
       </c>
       <c r="F3">
-        <v>2.58950700349765</v>
+        <v>2.861030927522078</v>
       </c>
       <c r="G3">
-        <v>-15.98069474648152</v>
+        <v>-18.56102938459752</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.53323881737216</v>
       </c>
       <c r="E4">
-        <v>-6.697500336438002</v>
+        <v>-8.391782130345181</v>
       </c>
       <c r="F4">
-        <v>2.857712487706463</v>
+        <v>2.880333544742112</v>
       </c>
       <c r="G4">
-        <v>-15.63825773756045</v>
+        <v>-18.03762730897113</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.38234292184585</v>
       </c>
       <c r="E5">
-        <v>-7.555437506230483</v>
+        <v>-8.215931009640617</v>
       </c>
       <c r="F5">
-        <v>2.577745843112703</v>
+        <v>3.074688418256543</v>
       </c>
       <c r="G5">
-        <v>-14.63408051861907</v>
+        <v>-17.36198880012004</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.17674254830904</v>
       </c>
       <c r="E6">
-        <v>-10.15327118991074</v>
+        <v>-9.461034692344938</v>
       </c>
       <c r="F6">
-        <v>3.026452584391528</v>
+        <v>3.371830432579948</v>
       </c>
       <c r="G6">
-        <v>-13.29753984876142</v>
+        <v>-16.55031744434898</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.992800345740164</v>
       </c>
       <c r="E7">
-        <v>-10.85442463219094</v>
+        <v>-9.773144370194478</v>
       </c>
       <c r="F7">
-        <v>2.96727070366592</v>
+        <v>3.097422133258973</v>
       </c>
       <c r="G7">
-        <v>-13.2885536658788</v>
+        <v>-15.84316333216627</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.860286936133733</v>
       </c>
       <c r="E8">
-        <v>-11.09954716458232</v>
+        <v>-10.59847052466441</v>
       </c>
       <c r="F8">
-        <v>2.614898121128261</v>
+        <v>3.703490516578009</v>
       </c>
       <c r="G8">
-        <v>-12.48847009997541</v>
+        <v>-15.21268939936914</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.812287746718216</v>
       </c>
       <c r="E9">
-        <v>-10.1989980465971</v>
+        <v>-10.78161053124405</v>
       </c>
       <c r="F9">
-        <v>2.980827764580137</v>
+        <v>3.887401333877944</v>
       </c>
       <c r="G9">
-        <v>-12.35841977428599</v>
+        <v>-13.99571691566759</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.85638951321627</v>
       </c>
       <c r="E10">
-        <v>-11.11282082797647</v>
+        <v>-12.05157949015012</v>
       </c>
       <c r="F10">
-        <v>3.566124006906572</v>
+        <v>3.841123760553147</v>
       </c>
       <c r="G10">
-        <v>-10.89685446207681</v>
+        <v>-13.54774186202305</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.98193867843871</v>
       </c>
       <c r="E11">
-        <v>-11.27306002731101</v>
+        <v>-12.34649902632619</v>
       </c>
       <c r="F11">
-        <v>3.587712918158333</v>
+        <v>3.924942944572817</v>
       </c>
       <c r="G11">
-        <v>-10.90733790698243</v>
+        <v>-13.0054092773665</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.178913495098788</v>
       </c>
       <c r="E12">
-        <v>-12.78543947161335</v>
+        <v>-13.09426811251627</v>
       </c>
       <c r="F12">
-        <v>3.965571052210522</v>
+        <v>4.464213437264907</v>
       </c>
       <c r="G12">
-        <v>-9.940151022780233</v>
+        <v>-11.82924534236864</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.41237676173404</v>
       </c>
       <c r="E13">
-        <v>-12.99695837117554</v>
+        <v>-13.76922309775946</v>
       </c>
       <c r="F13">
-        <v>4.181049294496341</v>
+        <v>4.498080410160962</v>
       </c>
       <c r="G13">
-        <v>-10.12295666442228</v>
+        <v>-11.47241138239987</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.66943686508169</v>
       </c>
       <c r="E14">
-        <v>-14.72206114632427</v>
+        <v>-14.72324481155185</v>
       </c>
       <c r="F14">
-        <v>4.258393958895731</v>
+        <v>4.699173224129764</v>
       </c>
       <c r="G14">
-        <v>-8.064105204658206</v>
+        <v>-10.81825277467216</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.922642953249385</v>
       </c>
       <c r="E15">
-        <v>-14.74883274652412</v>
+        <v>-15.16692822417196</v>
       </c>
       <c r="F15">
-        <v>4.042367337389258</v>
+        <v>4.685655924850882</v>
       </c>
       <c r="G15">
-        <v>-8.688853774567024</v>
+        <v>-10.50089066217643</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.159855898456199</v>
       </c>
       <c r="E16">
-        <v>-16.46694982022449</v>
+        <v>-16.53647873101344</v>
       </c>
       <c r="F16">
-        <v>4.471242963045063</v>
+        <v>5.201733786999391</v>
       </c>
       <c r="G16">
-        <v>-7.77555265872541</v>
+        <v>-9.414753032913936</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.376119236177765</v>
       </c>
       <c r="E17">
-        <v>-16.7082472449857</v>
+        <v>-17.43248838902063</v>
       </c>
       <c r="F17">
-        <v>5.234586838194419</v>
+        <v>5.410543671692673</v>
       </c>
       <c r="G17">
-        <v>-7.719531301289301</v>
+        <v>-8.671228637832417</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.5692335360063866</v>
       </c>
       <c r="E18">
-        <v>-18.56402250804751</v>
+        <v>-17.59370774622782</v>
       </c>
       <c r="F18">
-        <v>4.786224697755158</v>
+        <v>5.453991541969507</v>
       </c>
       <c r="G18">
-        <v>-6.365800183671467</v>
+        <v>-8.626079726246001</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.2425792834016092</v>
       </c>
       <c r="E19">
-        <v>-19.78882529379607</v>
+        <v>-18.39798542570352</v>
       </c>
       <c r="F19">
-        <v>5.581005115840755</v>
+        <v>5.760310210381125</v>
       </c>
       <c r="G19">
-        <v>-6.06301124748333</v>
+        <v>-7.702325189061569</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.04821461681444</v>
       </c>
       <c r="E20">
-        <v>-17.47787468237835</v>
+        <v>-19.951639484152</v>
       </c>
       <c r="F20">
-        <v>5.437801929449193</v>
+        <v>5.987897527361067</v>
       </c>
       <c r="G20">
-        <v>-6.817889770791599</v>
+        <v>-7.487081045874938</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.815690616890328</v>
       </c>
       <c r="E21">
-        <v>-20.32114238929935</v>
+        <v>-19.98885225762247</v>
       </c>
       <c r="F21">
-        <v>5.401524407410992</v>
+        <v>5.886720732783135</v>
       </c>
       <c r="G21">
-        <v>-6.102911257069314</v>
+        <v>-6.753307781841229</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>2.523779884536095</v>
       </c>
       <c r="E22">
-        <v>-19.59389016705392</v>
+        <v>-20.43485316216183</v>
       </c>
       <c r="F22">
-        <v>5.847179443177904</v>
+        <v>5.781269562406758</v>
       </c>
       <c r="G22">
-        <v>-6.299424613187003</v>
+        <v>-6.707959148293591</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.148161576605143</v>
       </c>
       <c r="E23">
-        <v>-21.61297385261932</v>
+        <v>-20.01708163499733</v>
       </c>
       <c r="F23">
-        <v>5.766756565509711</v>
+        <v>5.51772281647129</v>
       </c>
       <c r="G23">
-        <v>-5.583072847809793</v>
+        <v>-6.373765565418953</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.672953188793023</v>
       </c>
       <c r="E24">
-        <v>-21.54646432646351</v>
+        <v>-20.84063852144288</v>
       </c>
       <c r="F24">
-        <v>6.037183731092832</v>
+        <v>5.610383994148442</v>
       </c>
       <c r="G24">
-        <v>-5.04395670048949</v>
+        <v>-6.293096168298144</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>4.094779687735825</v>
       </c>
       <c r="E25">
-        <v>-20.98339685431121</v>
+        <v>-20.87989467488515</v>
       </c>
       <c r="F25">
-        <v>5.389243032297086</v>
+        <v>5.673836937202885</v>
       </c>
       <c r="G25">
-        <v>-4.785338952038399</v>
+        <v>-6.137887402356459</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>4.413449971369523</v>
       </c>
       <c r="E26">
-        <v>-20.06902584903695</v>
+        <v>-21.78674421445014</v>
       </c>
       <c r="F26">
-        <v>5.85312877786481</v>
+        <v>5.338590022350703</v>
       </c>
       <c r="G26">
-        <v>-4.968840357113979</v>
+        <v>-5.495592018050768</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>4.645532495449958</v>
       </c>
       <c r="E27">
-        <v>-20.85316876000988</v>
+        <v>-21.67913866223516</v>
       </c>
       <c r="F27">
-        <v>5.577245984566852</v>
+        <v>5.151584424433908</v>
       </c>
       <c r="G27">
-        <v>-5.240394345014036</v>
+        <v>-5.498281084979615</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>4.804511695068286</v>
       </c>
       <c r="E28">
-        <v>-19.70439050756231</v>
+        <v>-21.62927520706927</v>
       </c>
       <c r="F28">
-        <v>5.369377125243149</v>
+        <v>5.220779610324557</v>
       </c>
       <c r="G28">
-        <v>-4.745337123413361</v>
+        <v>-5.450295599394953</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>4.91326286858655</v>
       </c>
       <c r="E29">
-        <v>-22.04958434635324</v>
+        <v>-21.02472130699325</v>
       </c>
       <c r="F29">
-        <v>5.506316197334741</v>
+        <v>5.028333295306176</v>
       </c>
       <c r="G29">
-        <v>-4.926893523768562</v>
+        <v>-5.79595296176917</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>4.988810937399836</v>
       </c>
       <c r="E30">
-        <v>-21.57869739955551</v>
+        <v>-21.8900802654232</v>
       </c>
       <c r="F30">
-        <v>6.004271037444802</v>
+        <v>5.024749777921665</v>
       </c>
       <c r="G30">
-        <v>-5.271216795656719</v>
+        <v>-5.343978247411046</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>5.046251275619143</v>
       </c>
       <c r="E31">
-        <v>-21.28404366890422</v>
+        <v>-21.96141997634978</v>
       </c>
       <c r="F31">
-        <v>5.422649432917185</v>
+        <v>5.068156229828359</v>
       </c>
       <c r="G31">
-        <v>-5.123043986388085</v>
+        <v>-5.809912613097852</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>5.093913177985979</v>
       </c>
       <c r="E32">
-        <v>-20.37549131269605</v>
+        <v>-20.54625059631638</v>
       </c>
       <c r="F32">
-        <v>5.164422462442495</v>
+        <v>5.081163254787117</v>
       </c>
       <c r="G32">
-        <v>-4.91922315615987</v>
+        <v>-5.492934280057015</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>5.133109222007283</v>
       </c>
       <c r="E33">
-        <v>-20.59129632634547</v>
+        <v>-21.08634250341973</v>
       </c>
       <c r="F33">
-        <v>5.405856768927634</v>
+        <v>5.294991389206559</v>
       </c>
       <c r="G33">
-        <v>-5.556338823196793</v>
+        <v>-6.164287251661796</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>5.160285987819639</v>
       </c>
       <c r="E34">
-        <v>-18.84439334495271</v>
+        <v>-21.07957276896026</v>
       </c>
       <c r="F34">
-        <v>5.2723968399278</v>
+        <v>5.259186036587953</v>
       </c>
       <c r="G34">
-        <v>-5.447335015028631</v>
+        <v>-6.039522378397083</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>5.165186028378608</v>
       </c>
       <c r="E35">
-        <v>-19.48619324418979</v>
+        <v>-19.73609196960473</v>
       </c>
       <c r="F35">
-        <v>5.463434930361421</v>
+        <v>5.524386203859409</v>
       </c>
       <c r="G35">
-        <v>-5.706435751229077</v>
+        <v>-6.452735367810948</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>5.137559688445866</v>
       </c>
       <c r="E36">
-        <v>-18.58877149433216</v>
+        <v>-19.4332356465869</v>
       </c>
       <c r="F36">
-        <v>5.416633828838055</v>
+        <v>5.553375749487781</v>
       </c>
       <c r="G36">
-        <v>-6.196650041613236</v>
+        <v>-6.386088279889008</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>5.06489158255092</v>
       </c>
       <c r="E37">
-        <v>-18.94133345048554</v>
+        <v>-19.88746821597208</v>
       </c>
       <c r="F37">
-        <v>5.659201341930223</v>
+        <v>5.575395411788997</v>
       </c>
       <c r="G37">
-        <v>-6.153468326076223</v>
+        <v>-7.087308169616126</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>4.941729557397509</v>
       </c>
       <c r="E38">
-        <v>-18.20856576360074</v>
+        <v>-18.92509439420546</v>
       </c>
       <c r="F38">
-        <v>5.217406498260357</v>
+        <v>5.603031405081194</v>
       </c>
       <c r="G38">
-        <v>-5.987934065276685</v>
+        <v>-7.386053062432627</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>4.764567705784189</v>
       </c>
       <c r="E39">
-        <v>-18.45946125973363</v>
+        <v>-18.25941768306194</v>
       </c>
       <c r="F39">
-        <v>5.975233446507068</v>
+        <v>5.768196268055776</v>
       </c>
       <c r="G39">
-        <v>-5.728705402591274</v>
+        <v>-7.264086907369588</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>4.539589131273508</v>
       </c>
       <c r="E40">
-        <v>-18.20062897675899</v>
+        <v>-18.07472437544681</v>
       </c>
       <c r="F40">
-        <v>5.78462279365329</v>
+        <v>5.948513627562368</v>
       </c>
       <c r="G40">
-        <v>-6.985408197480383</v>
+        <v>-8.195765054388049</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>4.273833079125768</v>
       </c>
       <c r="E41">
-        <v>-16.71016187540645</v>
+        <v>-17.56740130569636</v>
       </c>
       <c r="F41">
-        <v>5.865259390111405</v>
+        <v>6.17333751088657</v>
       </c>
       <c r="G41">
-        <v>-7.056462222272122</v>
+        <v>-8.02138559091382</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>3.979356141545589</v>
       </c>
       <c r="E42">
-        <v>-15.66739434202512</v>
+        <v>-17.46454702723698</v>
       </c>
       <c r="F42">
-        <v>5.959756229953162</v>
+        <v>6.178373984695591</v>
       </c>
       <c r="G42">
-        <v>-6.945641335868545</v>
+        <v>-8.600181139902157</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>3.670099667295912</v>
       </c>
       <c r="E43">
-        <v>-15.97090271922094</v>
+        <v>-16.67083511737165</v>
       </c>
       <c r="F43">
-        <v>5.943967547255804</v>
+        <v>6.225039233964898</v>
       </c>
       <c r="G43">
-        <v>-7.101053739888337</v>
+        <v>-9.029213936165872</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>3.35733512614895</v>
       </c>
       <c r="E44">
-        <v>-14.7528115229733</v>
+        <v>-16.29840835145162</v>
       </c>
       <c r="F44">
-        <v>6.0219947863951</v>
+        <v>6.198814778727072</v>
       </c>
       <c r="G44">
-        <v>-7.339754117853825</v>
+        <v>-9.224243083983511</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>3.052973925199484</v>
       </c>
       <c r="E45">
-        <v>-13.41141563570283</v>
+        <v>-15.71554667412518</v>
       </c>
       <c r="F45">
-        <v>5.948175653662025</v>
+        <v>6.140565639697016</v>
       </c>
       <c r="G45">
-        <v>-7.085538084783351</v>
+        <v>-9.044468516811747</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>2.759109289757999</v>
       </c>
       <c r="E46">
-        <v>-14.20932644221756</v>
+        <v>-14.8097852759273</v>
       </c>
       <c r="F46">
-        <v>5.577660168268251</v>
+        <v>6.317163629565036</v>
       </c>
       <c r="G46">
-        <v>-7.06105452200789</v>
+        <v>-9.459468560898229</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>2.479924467624072</v>
       </c>
       <c r="E47">
-        <v>-12.46393938295837</v>
+        <v>-13.55917028179493</v>
       </c>
       <c r="F47">
-        <v>5.672243158319898</v>
+        <v>6.534492444628709</v>
       </c>
       <c r="G47">
-        <v>-7.626635787248308</v>
+        <v>-9.350685360648015</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>2.211952949785168</v>
       </c>
       <c r="E48">
-        <v>-11.73177391171567</v>
+        <v>-14.0878574706003</v>
       </c>
       <c r="F48">
-        <v>5.64144942848823</v>
+        <v>6.28822875618525</v>
       </c>
       <c r="G48">
-        <v>-7.540026946182715</v>
+        <v>-9.846840400349253</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>1.954157504979938</v>
       </c>
       <c r="E49">
-        <v>-12.88666569123339</v>
+        <v>-12.79203061798585</v>
       </c>
       <c r="F49">
-        <v>5.684196499942296</v>
+        <v>6.430688068649098</v>
       </c>
       <c r="G49">
-        <v>-7.898166278447045</v>
+        <v>-9.724855970074076</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>1.704196354492644</v>
       </c>
       <c r="E50">
-        <v>-11.44275608883218</v>
+        <v>-13.14968025801213</v>
       </c>
       <c r="F50">
-        <v>5.64122742602428</v>
+        <v>6.54443782366672</v>
       </c>
       <c r="G50">
-        <v>-7.902235123892296</v>
+        <v>-10.03427880826823</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>1.458609861852333</v>
       </c>
       <c r="E51">
-        <v>-12.00015858073741</v>
+        <v>-12.43339251366426</v>
       </c>
       <c r="F51">
-        <v>5.394950483702376</v>
+        <v>6.241228846485212</v>
       </c>
       <c r="G51">
-        <v>-8.26186258057356</v>
+        <v>-9.869672667170834</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>1.218253483917075</v>
       </c>
       <c r="E52">
-        <v>-11.34043342142238</v>
+        <v>-12.42974184090973</v>
       </c>
       <c r="F52">
-        <v>5.009489593627293</v>
+        <v>6.425091618475784</v>
       </c>
       <c r="G52">
-        <v>-7.84249345541385</v>
+        <v>-10.41016598226295</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>0.9784207348461199</v>
       </c>
       <c r="E53">
-        <v>-10.68602437260312</v>
+        <v>-11.37728071229625</v>
       </c>
       <c r="F53">
-        <v>5.806324362871832</v>
+        <v>5.865714992182945</v>
       </c>
       <c r="G53">
-        <v>-8.299676605231245</v>
+        <v>-11.20391457641601</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>0.7407526399421376</v>
       </c>
       <c r="E54">
-        <v>-9.86916246281319</v>
+        <v>-11.57056701414245</v>
       </c>
       <c r="F54">
-        <v>5.700752250854646</v>
+        <v>6.488334156209915</v>
       </c>
       <c r="G54">
-        <v>-8.81354424161089</v>
+        <v>-10.37207130256172</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.5009351766077238</v>
       </c>
       <c r="E55">
-        <v>-10.01534719502451</v>
+        <v>-11.09540641289147</v>
       </c>
       <c r="F55">
-        <v>5.438017304973921</v>
+        <v>6.294299032512965</v>
       </c>
       <c r="G55">
-        <v>-9.095154817675915</v>
+        <v>-11.02813836458553</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>0.2591918657643939</v>
       </c>
       <c r="E56">
-        <v>-9.527398856104375</v>
+        <v>-10.70746740267321</v>
       </c>
       <c r="F56">
-        <v>4.991946428770804</v>
+        <v>5.882628597813306</v>
       </c>
       <c r="G56">
-        <v>-8.342175611057682</v>
+        <v>-11.14577068362732</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.01435465129923437</v>
       </c>
       <c r="E57">
-        <v>-9.633849815571054</v>
+        <v>-10.55598317281141</v>
       </c>
       <c r="F57">
-        <v>5.460429613424065</v>
+        <v>6.09236791073253</v>
       </c>
       <c r="G57">
-        <v>-8.239149102630874</v>
+        <v>-11.01873185182375</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.2354177826227705</v>
       </c>
       <c r="E58">
-        <v>-9.840447159713325</v>
+        <v>-10.01285942144093</v>
       </c>
       <c r="F58">
-        <v>5.474472097636323</v>
+        <v>5.942797892483051</v>
       </c>
       <c r="G58">
-        <v>-9.747843576198829</v>
+        <v>-11.80098664291443</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.4895594741369939</v>
       </c>
       <c r="E59">
-        <v>-8.461875877874313</v>
+        <v>-9.517979372819664</v>
       </c>
       <c r="F59">
-        <v>5.155507572453567</v>
+        <v>6.17669902580713</v>
       </c>
       <c r="G59">
-        <v>-8.980034034930775</v>
+        <v>-11.88156988546374</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.7528714501282078</v>
       </c>
       <c r="E60">
-        <v>-7.753861330485492</v>
+        <v>-9.238858652523236</v>
       </c>
       <c r="F60">
-        <v>5.440691274950158</v>
+        <v>5.900132001034459</v>
       </c>
       <c r="G60">
-        <v>-9.438957246018147</v>
+        <v>-11.38485875716459</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.023386720504904</v>
       </c>
       <c r="E61">
-        <v>-7.83455822652691</v>
+        <v>-9.266377830761551</v>
       </c>
       <c r="F61">
-        <v>5.094160339337041</v>
+        <v>6.17090211072234</v>
       </c>
       <c r="G61">
-        <v>-9.787178359580837</v>
+        <v>-12.11821560743602</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.305086303678282</v>
       </c>
       <c r="E62">
-        <v>-8.431520056301141</v>
+        <v>-9.289062671017764</v>
       </c>
       <c r="F62">
-        <v>4.780870130863462</v>
+        <v>5.877954948926711</v>
       </c>
       <c r="G62">
-        <v>-9.854410254291185</v>
+        <v>-12.24095715364262</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.596196986867378</v>
       </c>
       <c r="E63">
-        <v>-7.478250073758545</v>
+        <v>-8.69230434859845</v>
       </c>
       <c r="F63">
-        <v>5.302463263179811</v>
+        <v>6.289921939156573</v>
       </c>
       <c r="G63">
-        <v>-9.79293244065965</v>
+        <v>-12.38935448694609</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.896491750673897</v>
       </c>
       <c r="E64">
-        <v>-7.029445751574923</v>
+        <v>-9.051893538313429</v>
       </c>
       <c r="F64">
-        <v>5.183478226176495</v>
+        <v>6.011095128109064</v>
       </c>
       <c r="G64">
-        <v>-10.02126555185383</v>
+        <v>-12.68565572282531</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.204272677549549</v>
       </c>
       <c r="E65">
-        <v>-7.283892243390543</v>
+        <v>-8.304668522806903</v>
       </c>
       <c r="F65">
-        <v>5.158324021623085</v>
+        <v>5.940753481732941</v>
       </c>
       <c r="G65">
-        <v>-10.08043024577764</v>
+        <v>-12.46101942597215</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.514501779725635</v>
       </c>
       <c r="E66">
-        <v>-8.212172353391646</v>
+        <v>-8.402975034865594</v>
       </c>
       <c r="F66">
-        <v>4.794488490965486</v>
+        <v>5.831210176386735</v>
       </c>
       <c r="G66">
-        <v>-10.25614641048252</v>
+        <v>-12.54818957712483</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.825398709341481</v>
       </c>
       <c r="E67">
-        <v>-6.809794864238715</v>
+        <v>-8.312111077500996</v>
       </c>
       <c r="F67">
-        <v>5.184414281341659</v>
+        <v>5.979708287216991</v>
       </c>
       <c r="G67">
-        <v>-11.07670604621401</v>
+        <v>-12.41905953890378</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.128589737803348</v>
       </c>
       <c r="E68">
-        <v>-7.371329801412159</v>
+        <v>-9.032813685487167</v>
       </c>
       <c r="F68">
-        <v>5.018116211760047</v>
+        <v>5.898047828649016</v>
       </c>
       <c r="G68">
-        <v>-10.39183986060563</v>
+        <v>-12.56595830481195</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.421260627309622</v>
       </c>
       <c r="E69">
-        <v>-6.968493222171739</v>
+        <v>-8.450504385266932</v>
       </c>
       <c r="F69">
-        <v>5.123360290285723</v>
+        <v>6.108623792645067</v>
       </c>
       <c r="G69">
-        <v>-11.04098844946299</v>
+        <v>-12.69127926667457</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.69618123455372</v>
       </c>
       <c r="E70">
-        <v>-7.064320267069508</v>
+        <v>-7.660800324330058</v>
       </c>
       <c r="F70">
-        <v>5.076270916906183</v>
+        <v>6.169223838364267</v>
       </c>
       <c r="G70">
-        <v>-10.13629626391057</v>
+        <v>-12.04319586161038</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.94985554501595</v>
       </c>
       <c r="E71">
-        <v>-7.141179595846785</v>
+        <v>-8.609289960637776</v>
       </c>
       <c r="F71">
-        <v>4.762125833272916</v>
+        <v>5.720725845670948</v>
       </c>
       <c r="G71">
-        <v>-10.32622271142488</v>
+        <v>-12.45417535902654</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.178399894586811</v>
       </c>
       <c r="E72">
-        <v>-7.116866696751239</v>
+        <v>-7.694374884679973</v>
       </c>
       <c r="F72">
-        <v>5.266300055843195</v>
+        <v>6.170868976026227</v>
       </c>
       <c r="G72">
-        <v>-10.06831639087487</v>
+        <v>-12.18642783674033</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.377363674151622</v>
       </c>
       <c r="E73">
-        <v>-8.417403291008048</v>
+        <v>-7.830542071175801</v>
       </c>
       <c r="F73">
-        <v>5.048248904404281</v>
+        <v>6.027584609629192</v>
       </c>
       <c r="G73">
-        <v>-9.465423669310557</v>
+        <v>-11.93303549358835</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.545986512094239</v>
       </c>
       <c r="E74">
-        <v>-7.69358992773958</v>
+        <v>-7.742485684666786</v>
       </c>
       <c r="F74">
-        <v>4.916755519618693</v>
+        <v>6.107649632579375</v>
       </c>
       <c r="G74">
-        <v>-9.714493924791947</v>
+        <v>-12.04826070611714</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.68119401091238</v>
       </c>
       <c r="E75">
-        <v>-7.813061204709598</v>
+        <v>-8.669212493632402</v>
       </c>
       <c r="F75">
-        <v>4.898538063696327</v>
+        <v>5.608793528735068</v>
       </c>
       <c r="G75">
-        <v>-10.04391376118173</v>
+        <v>-12.09489774212049</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.784430000292532</v>
       </c>
       <c r="E76">
-        <v>-7.861657930421416</v>
+        <v>-8.5590610228753</v>
       </c>
       <c r="F76">
-        <v>5.119352648790979</v>
+        <v>6.096494837133276</v>
       </c>
       <c r="G76">
-        <v>-10.7759952627204</v>
+        <v>-11.87464358006351</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.853756645445053</v>
       </c>
       <c r="E77">
-        <v>-8.072063769348555</v>
+        <v>-8.855899342683445</v>
       </c>
       <c r="F77">
-        <v>4.84818326601495</v>
+        <v>6.080326762165436</v>
       </c>
       <c r="G77">
-        <v>-9.902019792654727</v>
+        <v>-11.41714975163978</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.889806999289728</v>
       </c>
       <c r="E78">
-        <v>-8.248965652518303</v>
+        <v>-9.72730953001367</v>
       </c>
       <c r="F78">
-        <v>5.056171410244656</v>
+        <v>6.293783787988423</v>
       </c>
       <c r="G78">
-        <v>-9.171426415532995</v>
+        <v>-11.37390798897717</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.890031699693855</v>
       </c>
       <c r="E79">
-        <v>-8.750989224618277</v>
+        <v>-9.614994236156333</v>
       </c>
       <c r="F79">
-        <v>4.444852834326677</v>
+        <v>6.020801937335069</v>
       </c>
       <c r="G79">
-        <v>-9.785469627245952</v>
+        <v>-11.20814528802591</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.852822641124198</v>
       </c>
       <c r="E80">
-        <v>-10.14901830151411</v>
+        <v>-10.4667057421729</v>
       </c>
       <c r="F80">
-        <v>4.639386635200113</v>
+        <v>5.858882617844655</v>
       </c>
       <c r="G80">
-        <v>-8.314732769288195</v>
+        <v>-11.31275390767493</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.773617931326883</v>
       </c>
       <c r="E81">
-        <v>-8.351745173173834</v>
+        <v>-11.39012244171263</v>
       </c>
       <c r="F81">
-        <v>4.628536678958245</v>
+        <v>6.44935118623417</v>
       </c>
       <c r="G81">
-        <v>-9.401017905620089</v>
+        <v>-10.99628728057395</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.648066692586373</v>
       </c>
       <c r="E82">
-        <v>-10.58484799151897</v>
+        <v>-11.74170008678201</v>
       </c>
       <c r="F82">
-        <v>5.133905407323361</v>
+        <v>6.264426447233209</v>
       </c>
       <c r="G82">
-        <v>-8.88874021269643</v>
+        <v>-10.50110082711602</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.472144745901442</v>
       </c>
       <c r="E83">
-        <v>-12.07333401106957</v>
+        <v>-12.51204602973386</v>
       </c>
       <c r="F83">
-        <v>5.408989654445021</v>
+        <v>6.246576786437686</v>
       </c>
       <c r="G83">
-        <v>-8.909409477624274</v>
+        <v>-10.48357228793128</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.242125461022296</v>
       </c>
       <c r="E84">
-        <v>-13.26347409510111</v>
+        <v>-13.16955337420144</v>
       </c>
       <c r="F84">
-        <v>5.373308556936835</v>
+        <v>6.470048774160519</v>
       </c>
       <c r="G84">
-        <v>-9.157733060152605</v>
+        <v>-10.49629966781296</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.959735107090035</v>
       </c>
       <c r="E85">
-        <v>-14.33349500119596</v>
+        <v>-14.65441779347679</v>
       </c>
       <c r="F85">
-        <v>5.155691470016988</v>
+        <v>6.365767258556895</v>
       </c>
       <c r="G85">
-        <v>-8.513909084888818</v>
+        <v>-10.25393902593073</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.625237693250021</v>
       </c>
       <c r="E86">
-        <v>-16.84074299267038</v>
+        <v>-14.94500968345239</v>
       </c>
       <c r="F86">
-        <v>4.395072923622843</v>
+        <v>6.308636415520619</v>
       </c>
       <c r="G86">
-        <v>-8.7052831902789</v>
+        <v>-11.03331286036512</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.247768377511151</v>
       </c>
       <c r="E87">
-        <v>-15.78549505925794</v>
+        <v>-16.65442162621592</v>
       </c>
       <c r="F87">
-        <v>5.071685074964285</v>
+        <v>6.195436696458455</v>
       </c>
       <c r="G87">
-        <v>-8.337999725084195</v>
+        <v>-10.00648873746813</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.834854487644079</v>
       </c>
       <c r="E88">
-        <v>-18.10496806031421</v>
+        <v>-19.02178946027011</v>
       </c>
       <c r="F88">
-        <v>4.971780652717054</v>
+        <v>6.64993703935246</v>
       </c>
       <c r="G88">
-        <v>-7.403328359392024</v>
+        <v>-10.02221847362958</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.402033140322182</v>
       </c>
       <c r="E89">
-        <v>-18.85900434239346</v>
+        <v>-19.44865236702467</v>
       </c>
       <c r="F89">
-        <v>4.919724388390327</v>
+        <v>6.482943141152496</v>
       </c>
       <c r="G89">
-        <v>-7.391222336723032</v>
+        <v>-9.250223908781976</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.964661551215464</v>
       </c>
       <c r="E90">
-        <v>-21.15621613074865</v>
+        <v>-21.19306757483385</v>
       </c>
       <c r="F90">
-        <v>4.991126345042033</v>
+        <v>6.7650237793582</v>
       </c>
       <c r="G90">
-        <v>-7.311732996157406</v>
+        <v>-9.357948452100493</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.537984275148703</v>
       </c>
       <c r="E91">
-        <v>-22.79507331952599</v>
+        <v>-22.34010978494765</v>
       </c>
       <c r="F91">
-        <v>5.294348576101987</v>
+        <v>6.798922230215562</v>
       </c>
       <c r="G91">
-        <v>-7.292671949897687</v>
+        <v>-8.868241951539304</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.138662460418439</v>
       </c>
       <c r="E92">
-        <v>-24.23458051792289</v>
+        <v>-24.65567046093593</v>
       </c>
       <c r="F92">
-        <v>4.526940730474497</v>
+        <v>6.622504824441352</v>
       </c>
       <c r="G92">
-        <v>-7.93398830498171</v>
+        <v>-8.957996739837188</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.7746393820703343</v>
       </c>
       <c r="E93">
-        <v>-27.08731339345317</v>
+        <v>-27.39023616785219</v>
       </c>
       <c r="F93">
-        <v>5.193609159512733</v>
+        <v>6.38294262828654</v>
       </c>
       <c r="G93">
-        <v>-7.358841271559454</v>
+        <v>-9.105152664087584</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.4560694864248315</v>
       </c>
       <c r="E94">
-        <v>-29.68595695334176</v>
+        <v>-29.20464959933003</v>
       </c>
       <c r="F94">
-        <v>4.832626526190376</v>
+        <v>6.716708422222517</v>
       </c>
       <c r="G94">
-        <v>-7.582279236645293</v>
+        <v>-8.765163228220674</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.1819623912456445</v>
       </c>
       <c r="E95">
-        <v>-32.25885060301642</v>
+        <v>-31.18870925379315</v>
       </c>
       <c r="F95">
-        <v>4.762626167184206</v>
+        <v>6.333716067007777</v>
       </c>
       <c r="G95">
-        <v>-6.187379287570193</v>
+        <v>-8.546072152879038</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.04777313733221476</v>
       </c>
       <c r="E96">
-        <v>-33.80987775530195</v>
+        <v>-33.58857804306979</v>
       </c>
       <c r="F96">
-        <v>4.207222390955193</v>
+        <v>6.026229400558211</v>
       </c>
       <c r="G96">
-        <v>-6.848041260074366</v>
+        <v>-8.235706835887491</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.2401422560969758</v>
       </c>
       <c r="E97">
-        <v>-36.43318516064304</v>
+        <v>-35.75322555575344</v>
       </c>
       <c r="F97">
-        <v>4.969015562326509</v>
+        <v>5.732709008519846</v>
       </c>
       <c r="G97">
-        <v>-6.585664039412072</v>
+        <v>-8.074518159459862</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>0.4028313546345182</v>
       </c>
       <c r="E98">
-        <v>-39.22578784261245</v>
+        <v>-38.58450709479098</v>
       </c>
       <c r="F98">
-        <v>4.614456089845459</v>
+        <v>5.96662339572237</v>
       </c>
       <c r="G98">
-        <v>-6.653702654201076</v>
+        <v>-8.304245408265693</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.544832451755098</v>
       </c>
       <c r="E99">
-        <v>-42.09787468291643</v>
+        <v>-41.35711829404833</v>
       </c>
       <c r="F99">
-        <v>3.958105805176493</v>
+        <v>5.543770001084917</v>
       </c>
       <c r="G99">
-        <v>-7.398973637414048</v>
+        <v>-8.056686773902557</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>0.6743438630926208</v>
       </c>
       <c r="E100">
-        <v>-44.0157695277637</v>
+        <v>-43.55011355062959</v>
       </c>
       <c r="F100">
-        <v>4.013753870561758</v>
+        <v>5.566858257335745</v>
       </c>
       <c r="G100">
-        <v>-5.708824582529946</v>
+        <v>-8.08388420568048</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>0.7989756047406724</v>
       </c>
       <c r="E101">
-        <v>-46.29670072772556</v>
+        <v>-46.11023088396625</v>
       </c>
       <c r="F101">
-        <v>3.728291836617826</v>
+        <v>5.24217965380848</v>
       </c>
       <c r="G101">
-        <v>-6.693735811761206</v>
+        <v>-7.854921905039845</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>0.9181589967372232</v>
       </c>
       <c r="E102">
-        <v>-49.29837606778685</v>
+        <v>-48.8146494681784</v>
       </c>
       <c r="F102">
-        <v>3.503964973735303</v>
+        <v>4.667445095867738</v>
       </c>
       <c r="G102">
-        <v>-6.724500826022886</v>
+        <v>-7.615140678813636</v>
       </c>
     </row>
   </sheetData>
